--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/3.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/3.xlsx
@@ -426,13 +426,13 @@
         <v>-17.6670697140173</v>
       </c>
       <c r="E2">
-        <v>-11.34924552083502</v>
+        <v>-5.976971894367431</v>
       </c>
       <c r="F2">
-        <v>-2.238551535737919</v>
+        <v>-1.971183176416812</v>
       </c>
       <c r="G2">
-        <v>-11.19824918126151</v>
+        <v>-10.0758914798101</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.41266482306347</v>
       </c>
       <c r="E3">
-        <v>-12.3717206100789</v>
+        <v>-7.20431967619232</v>
       </c>
       <c r="F3">
-        <v>-1.988942854552549</v>
+        <v>-1.729381373541601</v>
       </c>
       <c r="G3">
-        <v>-11.03683360185773</v>
+        <v>-9.774125322268912</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.18222401394747</v>
       </c>
       <c r="E4">
-        <v>-13.12641797430121</v>
+        <v>-8.231037945581381</v>
       </c>
       <c r="F4">
-        <v>-2.61077389630844</v>
+        <v>-1.976950241507884</v>
       </c>
       <c r="G4">
-        <v>-10.19057208783599</v>
+        <v>-9.071336230828109</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.9863143399615</v>
       </c>
       <c r="E5">
-        <v>-13.52074390546712</v>
+        <v>-9.145015326075482</v>
       </c>
       <c r="F5">
-        <v>-2.272878361455068</v>
+        <v>-1.716786160396111</v>
       </c>
       <c r="G5">
-        <v>-10.00118239862537</v>
+        <v>-9.247510222245966</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.79846357171545</v>
       </c>
       <c r="E6">
-        <v>-14.53084720372204</v>
+        <v>-10.60832830301805</v>
       </c>
       <c r="F6">
-        <v>-1.906924308897856</v>
+        <v>-1.729292686010337</v>
       </c>
       <c r="G6">
-        <v>-10.15557300039482</v>
+        <v>-8.110241823685673</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.59709605462857</v>
       </c>
       <c r="E7">
-        <v>-14.36165888632147</v>
+        <v>-9.299631014119372</v>
       </c>
       <c r="F7">
-        <v>-2.387489574849506</v>
+        <v>-1.60351317850022</v>
       </c>
       <c r="G7">
-        <v>-9.468220982803636</v>
+        <v>-10.1013926120991</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.35548159046495</v>
       </c>
       <c r="E8">
-        <v>-16.35315042914867</v>
+        <v>-11.06269274257766</v>
       </c>
       <c r="F8">
-        <v>-2.048429224295328</v>
+        <v>-1.638479821407208</v>
       </c>
       <c r="G8">
-        <v>-9.836221224949021</v>
+        <v>-8.998788935880521</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.0534719782207</v>
       </c>
       <c r="E9">
-        <v>-16.49450221682409</v>
+        <v>-10.74950800868118</v>
       </c>
       <c r="F9">
-        <v>-1.819179874505891</v>
+        <v>-1.275982207010442</v>
       </c>
       <c r="G9">
-        <v>-9.835118813284444</v>
+        <v>-8.656528185302969</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.68334035250157</v>
       </c>
       <c r="E10">
-        <v>-17.61965592571788</v>
+        <v>-11.93434700499607</v>
       </c>
       <c r="F10">
-        <v>-1.750636290632714</v>
+        <v>-1.179811665295381</v>
       </c>
       <c r="G10">
-        <v>-9.339387792597359</v>
+        <v>-7.978521837769152</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.25858010750406</v>
       </c>
       <c r="E11">
-        <v>-18.28634692607513</v>
+        <v>-12.47580305667119</v>
       </c>
       <c r="F11">
-        <v>-1.363557976722412</v>
+        <v>-1.385257915175764</v>
       </c>
       <c r="G11">
-        <v>-8.598951177283965</v>
+        <v>-8.217245276605997</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.81393302273407</v>
       </c>
       <c r="E12">
-        <v>-18.48026071155758</v>
+        <v>-14.54786068056885</v>
       </c>
       <c r="F12">
-        <v>-1.649249021632196</v>
+        <v>-0.9511657074597266</v>
       </c>
       <c r="G12">
-        <v>-8.067307358586865</v>
+        <v>-7.508321744280925</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.3922504502502</v>
       </c>
       <c r="E13">
-        <v>-19.42994058112815</v>
+        <v>-14.31274231009061</v>
       </c>
       <c r="F13">
-        <v>-1.277009240296604</v>
+        <v>-0.8199065774821898</v>
       </c>
       <c r="G13">
-        <v>-7.910308046932468</v>
+        <v>-7.160909784844268</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.03270048504418</v>
       </c>
       <c r="E14">
-        <v>-19.33558529670433</v>
+        <v>-14.45469185633505</v>
       </c>
       <c r="F14">
-        <v>-1.196543518291999</v>
+        <v>-0.9156613963944473</v>
       </c>
       <c r="G14">
-        <v>-6.895831092969285</v>
+        <v>-6.667519319853447</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.75505592360172</v>
       </c>
       <c r="E15">
-        <v>-20.60373462933833</v>
+        <v>-16.17375493133481</v>
       </c>
       <c r="F15">
-        <v>-0.8307969312097091</v>
+        <v>-0.5219948658759176</v>
       </c>
       <c r="G15">
-        <v>-7.727628833529945</v>
+        <v>-5.897099093590874</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.5575703394447</v>
       </c>
       <c r="E16">
-        <v>-20.44413761988601</v>
+        <v>-16.4298039086765</v>
       </c>
       <c r="F16">
-        <v>-0.3407215112358453</v>
+        <v>-0.3814037487916538</v>
       </c>
       <c r="G16">
-        <v>-7.099535581091719</v>
+        <v>-5.350829284701275</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.41983983376242</v>
       </c>
       <c r="E17">
-        <v>-21.27881689203179</v>
+        <v>-17.14966825083181</v>
       </c>
       <c r="F17">
-        <v>-0.4748115155372301</v>
+        <v>-0.3596151228070378</v>
       </c>
       <c r="G17">
-        <v>-6.927367349776381</v>
+        <v>-5.03247729400834</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.31052991062322</v>
       </c>
       <c r="E18">
-        <v>-22.98246504150944</v>
+        <v>-17.95085492921687</v>
       </c>
       <c r="F18">
-        <v>-0.4576338493254161</v>
+        <v>-0.2043303822393269</v>
       </c>
       <c r="G18">
-        <v>-6.036946468806307</v>
+        <v>-5.57901525708662</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.19492129204841</v>
       </c>
       <c r="E19">
-        <v>-23.44436486181781</v>
+        <v>-19.50924774642449</v>
       </c>
       <c r="F19">
-        <v>0.09725235967893393</v>
+        <v>0.5594300080993742</v>
       </c>
       <c r="G19">
-        <v>-6.051403621176305</v>
+        <v>-4.245911537150741</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.04143363627805</v>
       </c>
       <c r="E20">
-        <v>-24.46901814705937</v>
+        <v>-20.61714344087504</v>
       </c>
       <c r="F20">
-        <v>0.1398176235682</v>
+        <v>0.746505269360659</v>
       </c>
       <c r="G20">
-        <v>-5.517713885335936</v>
+        <v>-5.152103857069904</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.82696773685674</v>
       </c>
       <c r="E21">
-        <v>-24.73763816824636</v>
+        <v>-20.84570458099018</v>
       </c>
       <c r="F21">
-        <v>0.2632009840282564</v>
+        <v>0.9183452797154161</v>
       </c>
       <c r="G21">
-        <v>-5.81213063177994</v>
+        <v>-4.645272577189642</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.53819139480556</v>
       </c>
       <c r="E22">
-        <v>-26.15283158038343</v>
+        <v>-22.60777910211479</v>
       </c>
       <c r="F22">
-        <v>0.3585725461089777</v>
+        <v>0.7334777045002541</v>
       </c>
       <c r="G22">
-        <v>-5.555331614298674</v>
+        <v>-3.961108614952781</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.17845117039733</v>
       </c>
       <c r="E23">
-        <v>-25.82286885028853</v>
+        <v>-22.02163154045797</v>
       </c>
       <c r="F23">
-        <v>0.5725557627265363</v>
+        <v>1.031307855251881</v>
       </c>
       <c r="G23">
-        <v>-5.762978962158381</v>
+        <v>-5.076451270406479</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.76664700618891</v>
       </c>
       <c r="E24">
-        <v>-26.23087982990562</v>
+        <v>-22.85251595138533</v>
       </c>
       <c r="F24">
-        <v>0.7340557571593894</v>
+        <v>1.113639974677832</v>
       </c>
       <c r="G24">
-        <v>-5.376419801719841</v>
+        <v>-4.006777590667027</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.33295848291239</v>
       </c>
       <c r="E25">
-        <v>-27.01308767372453</v>
+        <v>-23.18016915973631</v>
       </c>
       <c r="F25">
-        <v>0.6065515939073595</v>
+        <v>1.150291680678847</v>
       </c>
       <c r="G25">
-        <v>-5.493874646907644</v>
+        <v>-4.538772327191288</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.91124228681953</v>
       </c>
       <c r="E26">
-        <v>-26.51909455812381</v>
+        <v>-23.73446796369719</v>
       </c>
       <c r="F26">
-        <v>0.7290765857612478</v>
+        <v>0.7144573964558263</v>
       </c>
       <c r="G26">
-        <v>-5.541834520135065</v>
+        <v>-3.81053176164457</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.52961793874513</v>
       </c>
       <c r="E27">
-        <v>-26.42115272228591</v>
+        <v>-23.34923973681268</v>
       </c>
       <c r="F27">
-        <v>0.4379075020899591</v>
+        <v>0.9744322247107042</v>
       </c>
       <c r="G27">
-        <v>-5.092914613373274</v>
+        <v>-4.60562879435687</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.20599933673356</v>
       </c>
       <c r="E28">
-        <v>-27.04869053637284</v>
+        <v>-23.00195106516444</v>
       </c>
       <c r="F28">
-        <v>0.4692925940691803</v>
+        <v>0.7275831510829884</v>
       </c>
       <c r="G28">
-        <v>-5.921434913850057</v>
+        <v>-4.456899225459573</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.94842031476739</v>
       </c>
       <c r="E29">
-        <v>-28.15558996654171</v>
+        <v>-22.49929497878705</v>
       </c>
       <c r="F29">
-        <v>0.2579779219191372</v>
+        <v>0.9653971824631221</v>
       </c>
       <c r="G29">
-        <v>-5.515624931100655</v>
+        <v>-3.610505289616265</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.75738133558874</v>
       </c>
       <c r="E30">
-        <v>-27.59640946760057</v>
+        <v>-24.1291471158357</v>
       </c>
       <c r="F30">
-        <v>0.4213609426854477</v>
+        <v>0.2215091339513553</v>
       </c>
       <c r="G30">
-        <v>-4.79036716708482</v>
+        <v>-2.936226616359667</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.62752323007858</v>
       </c>
       <c r="E31">
-        <v>-26.87241968562427</v>
+        <v>-23.51255462342531</v>
       </c>
       <c r="F31">
-        <v>0.4042347469158856</v>
+        <v>0.4255181707134763</v>
       </c>
       <c r="G31">
-        <v>-4.527245007623546</v>
+        <v>-3.906090658635633</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.548937111535608</v>
       </c>
       <c r="E32">
-        <v>-27.6135497417196</v>
+        <v>-21.71414362686315</v>
       </c>
       <c r="F32">
-        <v>0.5516516364956934</v>
+        <v>0.3507070706799477</v>
       </c>
       <c r="G32">
-        <v>-5.008727440309609</v>
+        <v>-4.054436204250375</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.510166489496042</v>
       </c>
       <c r="E33">
-        <v>-26.82602999788969</v>
+        <v>-23.31767174450522</v>
       </c>
       <c r="F33">
-        <v>0.4168315437672909</v>
+        <v>0.4535956928883023</v>
       </c>
       <c r="G33">
-        <v>-4.979591329018483</v>
+        <v>-3.788510012717338</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.498490974381436</v>
       </c>
       <c r="E34">
-        <v>-26.62704432151865</v>
+        <v>-22.42856927173525</v>
       </c>
       <c r="F34">
-        <v>0.05937961641711499</v>
+        <v>0.5600619067596345</v>
       </c>
       <c r="G34">
-        <v>-4.657945345513973</v>
+        <v>-3.391400143645141</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.498312655981316</v>
       </c>
       <c r="E35">
-        <v>-26.17493053354086</v>
+        <v>-21.88803702875769</v>
       </c>
       <c r="F35">
-        <v>0.2038539804060363</v>
+        <v>0.57292951732258</v>
       </c>
       <c r="G35">
-        <v>-4.755139652001436</v>
+        <v>-3.076851969776829</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.491966344689706</v>
       </c>
       <c r="E36">
-        <v>-25.91081181551749</v>
+        <v>-23.10725619973881</v>
       </c>
       <c r="F36">
-        <v>0.1270212797714492</v>
+        <v>0.5316533900484818</v>
       </c>
       <c r="G36">
-        <v>-3.965601025249571</v>
+        <v>-2.918713830456923</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.46453221520745</v>
       </c>
       <c r="E37">
-        <v>-25.14535026857895</v>
+        <v>-21.45813993426153</v>
       </c>
       <c r="F37">
-        <v>0.4856894932646826</v>
+        <v>0.7810348094349852</v>
       </c>
       <c r="G37">
-        <v>-4.116330163652589</v>
+        <v>-2.394290311580974</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.406579269539488</v>
       </c>
       <c r="E38">
-        <v>-25.16628540391641</v>
+        <v>-20.50201604617804</v>
       </c>
       <c r="F38">
-        <v>0.2766007197787896</v>
+        <v>0.50041083160165</v>
       </c>
       <c r="G38">
-        <v>-4.110904179513724</v>
+        <v>-2.980382672762466</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.314397208630979</v>
       </c>
       <c r="E39">
-        <v>-25.17738922218322</v>
+        <v>-20.09065852426928</v>
       </c>
       <c r="F39">
-        <v>0.6192259923486214</v>
+        <v>0.7895361427890641</v>
       </c>
       <c r="G39">
-        <v>-4.00571821609446</v>
+        <v>-2.057276775683167</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.19053434095524</v>
       </c>
       <c r="E40">
-        <v>-24.33128913859009</v>
+        <v>-20.51191529035881</v>
       </c>
       <c r="F40">
-        <v>0.3920180394841856</v>
+        <v>0.7291462688215271</v>
       </c>
       <c r="G40">
-        <v>-3.872958718878607</v>
+        <v>-3.102992037354914</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.039842015128785</v>
       </c>
       <c r="E41">
-        <v>-25.29158375123464</v>
+        <v>-19.97966109786727</v>
       </c>
       <c r="F41">
-        <v>0.5008962374647322</v>
+        <v>0.7112408897415687</v>
       </c>
       <c r="G41">
-        <v>-3.987510215628468</v>
+        <v>-2.933902613391099</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.868074949188392</v>
       </c>
       <c r="E42">
-        <v>-24.34288203204972</v>
+        <v>-20.61734269373138</v>
       </c>
       <c r="F42">
-        <v>0.4999499731802571</v>
+        <v>0.8615377485286032</v>
       </c>
       <c r="G42">
-        <v>-4.256872753431268</v>
+        <v>-2.843584309988702</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.680357494135865</v>
       </c>
       <c r="E43">
-        <v>-23.11838266037566</v>
+        <v>-19.60219014695791</v>
       </c>
       <c r="F43">
-        <v>0.5715960369417801</v>
+        <v>0.9005365066962996</v>
       </c>
       <c r="G43">
-        <v>-4.189195270971948</v>
+        <v>-3.218487039583468</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.481491738739019</v>
       </c>
       <c r="E44">
-        <v>-23.3544429534475</v>
+        <v>-19.23357689120755</v>
       </c>
       <c r="F44">
-        <v>0.6621602597161849</v>
+        <v>0.5764706837495026</v>
       </c>
       <c r="G44">
-        <v>-4.663146212556168</v>
+        <v>-2.910662583705415</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.276025045402964</v>
       </c>
       <c r="E45">
-        <v>-23.96094147729479</v>
+        <v>-19.19598149999587</v>
       </c>
       <c r="F45">
-        <v>0.6751403133991265</v>
+        <v>0.6621792641871701</v>
       </c>
       <c r="G45">
-        <v>-4.684535647285399</v>
+        <v>-2.907676471628992</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.069602574297758</v>
       </c>
       <c r="E46">
-        <v>-23.80657938379533</v>
+        <v>-18.58559754545</v>
       </c>
       <c r="F46">
-        <v>0.6378218672077114</v>
+        <v>1.033265315763364</v>
       </c>
       <c r="G46">
-        <v>-4.742364256765388</v>
+        <v>-3.510288455051448</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.869935183747794</v>
       </c>
       <c r="E47">
-        <v>-22.9027955982925</v>
+        <v>-18.4675809843361</v>
       </c>
       <c r="F47">
-        <v>0.578526334027743</v>
+        <v>0.9141405405099244</v>
       </c>
       <c r="G47">
-        <v>-5.160092203456165</v>
+        <v>-3.559469919582861</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.684342910578532</v>
       </c>
       <c r="E48">
-        <v>-21.87644866377206</v>
+        <v>-17.45894038318566</v>
       </c>
       <c r="F48">
-        <v>0.7061635285766699</v>
+        <v>1.042721623784453</v>
       </c>
       <c r="G48">
-        <v>-6.207164788799013</v>
+        <v>-3.830222886512155</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.519763973584821</v>
       </c>
       <c r="E49">
-        <v>-22.30587479697143</v>
+        <v>-17.85909446039944</v>
       </c>
       <c r="F49">
-        <v>0.4883912955564224</v>
+        <v>0.6153490802676257</v>
       </c>
       <c r="G49">
-        <v>-5.290468107883743</v>
+        <v>-4.530750875349634</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.380848011512132</v>
       </c>
       <c r="E50">
-        <v>-22.07580114653773</v>
+        <v>-18.24711222727267</v>
       </c>
       <c r="F50">
-        <v>0.8860820228060837</v>
+        <v>0.9124475588863197</v>
       </c>
       <c r="G50">
-        <v>-5.523520582211817</v>
+        <v>-4.341712103966171</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.272501903905012</v>
       </c>
       <c r="E51">
-        <v>-21.00577255173931</v>
+        <v>-17.77415840191158</v>
       </c>
       <c r="F51">
-        <v>0.9807322068423223</v>
+        <v>0.886637903582403</v>
       </c>
       <c r="G51">
-        <v>-6.355411018047578</v>
+        <v>-4.137107147457055</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.197510820228961</v>
       </c>
       <c r="E52">
-        <v>-20.51040730851425</v>
+        <v>-15.29605968459016</v>
       </c>
       <c r="F52">
-        <v>0.6380910972133361</v>
+        <v>1.069220191161586</v>
       </c>
       <c r="G52">
-        <v>-5.81985413452306</v>
+        <v>-4.597292840688985</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.157200210356141</v>
       </c>
       <c r="E53">
-        <v>-21.45908638532913</v>
+        <v>-17.29648590663449</v>
       </c>
       <c r="F53">
-        <v>0.6198626421266281</v>
+        <v>1.022855616781181</v>
       </c>
       <c r="G53">
-        <v>-6.171076531875419</v>
+        <v>-4.729820599717089</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.151957637279022</v>
       </c>
       <c r="E54">
-        <v>-19.86176227707757</v>
+        <v>-15.67917764258709</v>
       </c>
       <c r="F54">
-        <v>0.9257681093410809</v>
+        <v>0.8913114197388649</v>
       </c>
       <c r="G54">
-        <v>-6.756139313394198</v>
+        <v>-4.579449000232313</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.180941367576276</v>
       </c>
       <c r="E55">
-        <v>-20.71069718539951</v>
+        <v>-15.38160255859505</v>
       </c>
       <c r="F55">
-        <v>0.6790900759522325</v>
+        <v>0.903193965222407</v>
       </c>
       <c r="G55">
-        <v>-6.414441355558322</v>
+        <v>-5.439257266600747</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.242403203631273</v>
       </c>
       <c r="E56">
-        <v>-20.07927846908801</v>
+        <v>-16.43096772649647</v>
       </c>
       <c r="F56">
-        <v>0.5224409727383704</v>
+        <v>0.7561136131496301</v>
       </c>
       <c r="G56">
-        <v>-6.814342014520125</v>
+        <v>-5.261345238774775</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.332668723721274</v>
       </c>
       <c r="E57">
-        <v>-20.00203175946517</v>
+        <v>-15.16935298185554</v>
       </c>
       <c r="F57">
-        <v>0.3689418605903175</v>
+        <v>0.5945027593026962</v>
       </c>
       <c r="G57">
-        <v>-6.64079659626045</v>
+        <v>-5.329760972889353</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.449162348476502</v>
       </c>
       <c r="E58">
-        <v>-19.96651946629701</v>
+        <v>-14.58120836316134</v>
       </c>
       <c r="F58">
-        <v>0.5549964233891015</v>
+        <v>0.7387989563761306</v>
       </c>
       <c r="G58">
-        <v>-6.820466523767776</v>
+        <v>-5.473322780199848</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.589960745389323</v>
       </c>
       <c r="E59">
-        <v>-19.52036062163931</v>
+        <v>-13.60572977716907</v>
       </c>
       <c r="F59">
-        <v>0.6513514668433106</v>
+        <v>0.3859302739452364</v>
       </c>
       <c r="G59">
-        <v>-6.255948987865714</v>
+        <v>-5.551097426553946</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.756537163629009</v>
       </c>
       <c r="E60">
-        <v>-19.72887420732249</v>
+        <v>-14.19096711555035</v>
       </c>
       <c r="F60">
-        <v>0.3577593131213995</v>
+        <v>0.5395576662724401</v>
       </c>
       <c r="G60">
-        <v>-6.946664519724794</v>
+        <v>-6.361787128756213</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.950301202741301</v>
       </c>
       <c r="E61">
-        <v>-19.67791076084017</v>
+        <v>-14.19934026399053</v>
       </c>
       <c r="F61">
-        <v>0.3642802222282214</v>
+        <v>0.346160250996721</v>
       </c>
       <c r="G61">
-        <v>-7.5808425548642</v>
+        <v>-5.447546872631083</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.17109145804846</v>
       </c>
       <c r="E62">
-        <v>-19.74424837657853</v>
+        <v>-15.06883444430728</v>
       </c>
       <c r="F62">
-        <v>0.5888251735958457</v>
+        <v>0.8231027896668033</v>
       </c>
       <c r="G62">
-        <v>-7.593594776281472</v>
+        <v>-5.434069641740709</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.416469745462356</v>
       </c>
       <c r="E63">
-        <v>-18.7351458710793</v>
+        <v>-13.92724690323966</v>
       </c>
       <c r="F63">
-        <v>-0.05081701673803492</v>
+        <v>-0.01589709315555283</v>
       </c>
       <c r="G63">
-        <v>-7.724113034167239</v>
+        <v>-6.509086541980546</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.681722734966529</v>
       </c>
       <c r="E64">
-        <v>-18.99605390103123</v>
+        <v>-13.34525195224787</v>
       </c>
       <c r="F64">
-        <v>0.07324496170678735</v>
+        <v>0.7138983482676762</v>
       </c>
       <c r="G64">
-        <v>-8.809654158676418</v>
+        <v>-6.657110964677979</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.958959346303663</v>
       </c>
       <c r="E65">
-        <v>-18.33855570290956</v>
+        <v>-13.63571280357385</v>
       </c>
       <c r="F65">
-        <v>0.4414375825754736</v>
+        <v>0.4339989158906545</v>
       </c>
       <c r="G65">
-        <v>-8.143549222356281</v>
+        <v>-7.769954158249528</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.237532613610872</v>
       </c>
       <c r="E66">
-        <v>-19.68072294319893</v>
+        <v>-13.68375991279524</v>
       </c>
       <c r="F66">
-        <v>0.4041555616201136</v>
+        <v>0.4074417513946504</v>
       </c>
       <c r="G66">
-        <v>-8.152653222589276</v>
+        <v>-6.533435604421886</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.508170610116034</v>
       </c>
       <c r="E67">
-        <v>-18.34822399491593</v>
+        <v>-13.5458225945216</v>
       </c>
       <c r="F67">
-        <v>0.05657170582904085</v>
+        <v>0.2419809084672833</v>
       </c>
       <c r="G67">
-        <v>-8.277090008319401</v>
+        <v>-7.07554736811416</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.762289017139105</v>
       </c>
       <c r="E68">
-        <v>-17.98645326339117</v>
+        <v>-13.06646550691366</v>
       </c>
       <c r="F68">
-        <v>0.08731777247138228</v>
+        <v>0.07522063483629807</v>
       </c>
       <c r="G68">
-        <v>-8.401864469694534</v>
+        <v>-6.517111304367739</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.993356963494923</v>
       </c>
       <c r="E69">
-        <v>-18.35661978572616</v>
+        <v>-14.04111085368852</v>
       </c>
       <c r="F69">
-        <v>0.1149645266372087</v>
+        <v>0.5214606587767134</v>
       </c>
       <c r="G69">
-        <v>-8.521408269117616</v>
+        <v>-7.962843094095163</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.19667690178892</v>
       </c>
       <c r="E70">
-        <v>-18.57851954057601</v>
+        <v>-12.91874668478345</v>
       </c>
       <c r="F70">
-        <v>-0.03120677824010596</v>
+        <v>0.02173096754233073</v>
       </c>
       <c r="G70">
-        <v>-9.00983291579953</v>
+        <v>-7.781766184733647</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.37055378086318</v>
       </c>
       <c r="E71">
-        <v>-18.13627329746093</v>
+        <v>-13.38890644168181</v>
       </c>
       <c r="F71">
-        <v>0.1266332718221666</v>
+        <v>0.5018789269852624</v>
       </c>
       <c r="G71">
-        <v>-8.954328309288108</v>
+        <v>-7.574956404895376</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.51654483747884</v>
       </c>
       <c r="E72">
-        <v>-19.19769326317077</v>
+        <v>-13.77066585747644</v>
       </c>
       <c r="F72">
-        <v>0.1761692172982393</v>
+        <v>0.3700298665542244</v>
       </c>
       <c r="G72">
-        <v>-9.500300169079173</v>
+        <v>-8.110159060047192</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.637923367085</v>
       </c>
       <c r="E73">
-        <v>-18.32082672716953</v>
+        <v>-13.31340319455192</v>
       </c>
       <c r="F73">
-        <v>-0.06226008383004265</v>
+        <v>0.5641003568440052</v>
       </c>
       <c r="G73">
-        <v>-9.509275058036138</v>
+        <v>-6.998166676679236</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.73796548987453</v>
       </c>
       <c r="E74">
-        <v>-18.93933929255917</v>
+        <v>-13.80568454697775</v>
       </c>
       <c r="F74">
-        <v>-0.2287835934266697</v>
+        <v>0.21109310014551</v>
       </c>
       <c r="G74">
-        <v>-9.473968089859811</v>
+        <v>-8.094059877089716</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.81880269028177</v>
       </c>
       <c r="E75">
-        <v>-19.42765823022829</v>
+        <v>-15.44238826520001</v>
       </c>
       <c r="F75">
-        <v>-0.0520364702929233</v>
+        <v>-0.04810016924009855</v>
       </c>
       <c r="G75">
-        <v>-9.522861536929307</v>
+        <v>-7.422108517347225</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.88149242150978</v>
       </c>
       <c r="E76">
-        <v>-19.48689519872262</v>
+        <v>-14.12867342710083</v>
       </c>
       <c r="F76">
-        <v>0.01645564313800193</v>
+        <v>0.1862970166274746</v>
       </c>
       <c r="G76">
-        <v>-9.617493481169374</v>
+        <v>-8.052244376383181</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.9257936816737</v>
       </c>
       <c r="E77">
-        <v>-19.09899517217359</v>
+        <v>-15.03003447900957</v>
       </c>
       <c r="F77">
-        <v>-0.4618290862954152</v>
+        <v>0.5064487104042629</v>
       </c>
       <c r="G77">
-        <v>-9.449370736503026</v>
+        <v>-8.06252030973708</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.95036535623522</v>
       </c>
       <c r="E78">
-        <v>-20.56022957954664</v>
+        <v>-15.07036959699589</v>
       </c>
       <c r="F78">
-        <v>-0.1787907487939926</v>
+        <v>-0.01377888649365256</v>
       </c>
       <c r="G78">
-        <v>-9.334703370659289</v>
+        <v>-8.583451203069098</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.95221565090439</v>
       </c>
       <c r="E79">
-        <v>-21.0507538840575</v>
+        <v>-15.74063356334518</v>
       </c>
       <c r="F79">
-        <v>-0.1859451402669903</v>
+        <v>0.1019092469232836</v>
       </c>
       <c r="G79">
-        <v>-10.03575111514643</v>
+        <v>-8.168888137913862</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.92769667591263</v>
       </c>
       <c r="E80">
-        <v>-21.44405185162367</v>
+        <v>-14.60805768555282</v>
       </c>
       <c r="F80">
-        <v>-0.2013601417949202</v>
+        <v>-0.1183596984726542</v>
       </c>
       <c r="G80">
-        <v>-10.17624073619649</v>
+        <v>-8.019801030098323</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.87391613429516</v>
       </c>
       <c r="E81">
-        <v>-20.98188937982285</v>
+        <v>-17.12649604933456</v>
       </c>
       <c r="F81">
-        <v>-0.4769518940819465</v>
+        <v>-0.1504772544377662</v>
       </c>
       <c r="G81">
-        <v>-10.67382566238556</v>
+        <v>-7.942158805565796</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.79059608478861</v>
       </c>
       <c r="E82">
-        <v>-22.13949866192962</v>
+        <v>-17.02379931578862</v>
       </c>
       <c r="F82">
-        <v>-0.332209883793316</v>
+        <v>-0.1664505123008884</v>
       </c>
       <c r="G82">
-        <v>-9.814639778578512</v>
+        <v>-7.990025983518119</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.67968087560434</v>
       </c>
       <c r="E83">
-        <v>-22.27541628079584</v>
+        <v>-18.0987096055673</v>
       </c>
       <c r="F83">
-        <v>-0.5431713895242162</v>
+        <v>-0.1219404575474628</v>
       </c>
       <c r="G83">
-        <v>-10.01102133996808</v>
+        <v>-8.087518239104115</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.54515889118098</v>
       </c>
       <c r="E84">
-        <v>-22.86179026615304</v>
+        <v>-19.75056559781923</v>
       </c>
       <c r="F84">
-        <v>-0.2573188066110576</v>
+        <v>-0.2003964567453753</v>
       </c>
       <c r="G84">
-        <v>-10.30289558743792</v>
+        <v>-8.414812013298622</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.39226982857933</v>
       </c>
       <c r="E85">
-        <v>-24.78991940066492</v>
+        <v>-19.59513931292797</v>
       </c>
       <c r="F85">
-        <v>-0.1612717939574015</v>
+        <v>-0.1693344407729037</v>
       </c>
       <c r="G85">
-        <v>-9.938464113383873</v>
+        <v>-8.474765993014824</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.22801136979013</v>
       </c>
       <c r="E86">
-        <v>-24.9424067059252</v>
+        <v>-21.08126221344717</v>
       </c>
       <c r="F86">
-        <v>-0.1004511519808649</v>
+        <v>0.06877811917229039</v>
       </c>
       <c r="G86">
-        <v>-9.741691907620671</v>
+        <v>-7.997299252067897</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.05954998052387</v>
       </c>
       <c r="E87">
-        <v>-26.60547972829412</v>
+        <v>-21.63389453897322</v>
       </c>
       <c r="F87">
-        <v>-0.2211192486489005</v>
+        <v>-0.3272536761309482</v>
       </c>
       <c r="G87">
-        <v>-9.985308332764559</v>
+        <v>-8.085124714679223</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.894287086720242</v>
       </c>
       <c r="E88">
-        <v>-28.70660562684703</v>
+        <v>-23.09433646339493</v>
       </c>
       <c r="F88">
-        <v>0.07412471034281397</v>
+        <v>0.1562224412932795</v>
       </c>
       <c r="G88">
-        <v>-10.49629765784215</v>
+        <v>-7.262106540888709</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.737882032972534</v>
       </c>
       <c r="E89">
-        <v>-29.90031137526893</v>
+        <v>-26.27463847424174</v>
       </c>
       <c r="F89">
-        <v>0.1592623647979655</v>
+        <v>-0.3614981491404954</v>
       </c>
       <c r="G89">
-        <v>-9.354513675166288</v>
+        <v>-7.718879061669652</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.593850439980894</v>
       </c>
       <c r="E90">
-        <v>-30.32409050138073</v>
+        <v>-26.74366611263819</v>
       </c>
       <c r="F90">
-        <v>0.209287675401909</v>
+        <v>-0.1767794422813845</v>
       </c>
       <c r="G90">
-        <v>-9.737057143865691</v>
+        <v>-8.216516956587357</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.464140069981076</v>
       </c>
       <c r="E91">
-        <v>-33.25332485629428</v>
+        <v>-27.56496827256531</v>
       </c>
       <c r="F91">
-        <v>0.230480036109362</v>
+        <v>-0.0539234558911694</v>
       </c>
       <c r="G91">
-        <v>-9.990740937994504</v>
+        <v>-7.752097075610698</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.349942036870003</v>
       </c>
       <c r="E92">
-        <v>-34.92748584727099</v>
+        <v>-29.6778953743822</v>
       </c>
       <c r="F92">
-        <v>0.2682506303396351</v>
+        <v>0.4885575846775435</v>
       </c>
       <c r="G92">
-        <v>-9.707871374391477</v>
+        <v>-8.379932105496861</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.253246940357094</v>
       </c>
       <c r="E93">
-        <v>-37.44215878491536</v>
+        <v>-33.4385960491331</v>
       </c>
       <c r="F93">
-        <v>0.2530921891700064</v>
+        <v>0.2044035263586938</v>
       </c>
       <c r="G93">
-        <v>-9.624962071905969</v>
+        <v>-6.924483864611677</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.175811607123668</v>
       </c>
       <c r="E94">
-        <v>-38.23180917576587</v>
+        <v>-33.69870706765968</v>
       </c>
       <c r="F94">
-        <v>0.6211676158009501</v>
+        <v>0.3616758178502813</v>
       </c>
       <c r="G94">
-        <v>-9.33610704196794</v>
+        <v>-8.00469501080263</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.121115380289091</v>
       </c>
       <c r="E95">
-        <v>-41.96345063280955</v>
+        <v>-37.29127682369079</v>
       </c>
       <c r="F95">
-        <v>0.5420290393534832</v>
+        <v>0.4888157287417601</v>
       </c>
       <c r="G95">
-        <v>-9.815702463696619</v>
+        <v>-7.335570856950676</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.090661843154159</v>
       </c>
       <c r="E96">
-        <v>-42.8868449750026</v>
+        <v>-39.30560998941269</v>
       </c>
       <c r="F96">
-        <v>0.9205133731136528</v>
+        <v>0.8550366357457243</v>
       </c>
       <c r="G96">
-        <v>-9.287203663261826</v>
+        <v>-7.664930411561688</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.083999681380512</v>
       </c>
       <c r="E97">
-        <v>-45.70523813586742</v>
+        <v>-42.53275906386885</v>
       </c>
       <c r="F97">
-        <v>0.9180934704748613</v>
+        <v>0.9085880675703937</v>
       </c>
       <c r="G97">
-        <v>-9.951441451897816</v>
+        <v>-6.632152761857413</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.096159285732151</v>
       </c>
       <c r="E98">
-        <v>-47.64123322973062</v>
+        <v>-43.25246490943389</v>
       </c>
       <c r="F98">
-        <v>1.160598438776527</v>
+        <v>0.9648286320394794</v>
       </c>
       <c r="G98">
-        <v>-10.03028209391556</v>
+        <v>-8.439945675032769</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.116574694636661</v>
       </c>
       <c r="E99">
-        <v>-49.98139236454139</v>
+        <v>-47.43762398139774</v>
       </c>
       <c r="F99">
-        <v>1.141948717916312</v>
+        <v>0.997766547668789</v>
       </c>
       <c r="G99">
-        <v>-9.478758449255135</v>
+        <v>-8.298731044509617</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.131968747050955</v>
       </c>
       <c r="E100">
-        <v>-52.62116666088466</v>
+        <v>-48.97086565396675</v>
       </c>
       <c r="F100">
-        <v>1.115269608064819</v>
+        <v>1.353037711973405</v>
       </c>
       <c r="G100">
-        <v>-9.578617744901711</v>
+        <v>-8.30412723373863</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.127744274031752</v>
       </c>
       <c r="E101">
-        <v>-54.23279282217094</v>
+        <v>-51.93177442032696</v>
       </c>
       <c r="F101">
-        <v>1.266109677980849</v>
+        <v>1.216840586951528</v>
       </c>
       <c r="G101">
-        <v>-9.919474824170612</v>
+        <v>-7.714396583009478</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.095275895132676</v>
       </c>
       <c r="E102">
-        <v>-57.71617314504761</v>
+        <v>-54.35421819209411</v>
       </c>
       <c r="F102">
-        <v>1.615612985341434</v>
+        <v>1.643644580044713</v>
       </c>
       <c r="G102">
-        <v>-9.662646011779493</v>
+        <v>-7.925106185493011</v>
       </c>
     </row>
   </sheetData>
